--- a/food_beverage_order_forms/031_food_online_order_form--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/031_food_online_order_form--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,8 +842,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -871,12 +871,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'meal1',_'value':_'meal1'}</t>
+          <t>meal1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'meal1', 'value': 'meal1'}</t>
+          <t>meal1</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'meal2',_'value':_'meal2'}</t>
+          <t>meal2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'meal2', 'value': 'meal2'}</t>
+          <t>meal2</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'meal3',_'value':_'meal3'}</t>
+          <t>meal3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'meal3', 'value': 'meal3'}</t>
+          <t>meal3</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'diet_type1',_'value':_'diet_type1'}</t>
+          <t>diet_type1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'diet_type1', 'value': 'diet_type1'}</t>
+          <t>diet type1</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'diet_type2',_'value':_'diet_type2'}</t>
+          <t>diet_type2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'diet_type2', 'value': 'diet_type2'}</t>
+          <t>diet type2</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'texture1',_'value':_'texture1'}</t>
+          <t>texture1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'texture1', 'value': 'texture1'}</t>
+          <t>texture1</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'texture2',_'value':_'texture2'}</t>
+          <t>texture2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'texture2', 'value': 'texture2'}</t>
+          <t>texture2</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'temperature1',_'value':_'temperature1'}</t>
+          <t>temperature1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'temperature1', 'value': 'temperature1'}</t>
+          <t>temperature1</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'temperature2',_'value':_'temperature2'}</t>
+          <t>temperature2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'temperature2', 'value': 'temperature2'}</t>
+          <t>temperature2</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'quantity1',_'value':_'quantity1'}</t>
+          <t>quantity1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'quantity1', 'value': 'quantity1'}</t>
+          <t>quantity1</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'quantity2',_'value':_'quantity2'}</t>
+          <t>quantity2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'quantity2', 'value': 'quantity2'}</t>
+          <t>quantity2</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'delivery1',_'value':_'delivery1'}</t>
+          <t>delivery1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'delivery1', 'value': 'delivery1'}</t>
+          <t>delivery1</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'delivery2',_'value':_'delivery2'}</t>
+          <t>delivery2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'delivery2', 'value': 'delivery2'}</t>
+          <t>delivery2</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'payment1',_'value':_'payment1'}</t>
+          <t>payment1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'payment1', 'value': 'payment1'}</t>
+          <t>payment1</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'payment2',_'value':_'payment2'}</t>
+          <t>payment2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'payment2', 'value': 'payment2'}</t>
+          <t>payment2</t>
         </is>
       </c>
     </row>
